--- a/www/download/COUNTRY.NLD.WIOD16.xlsx
+++ b/www/download/COUNTRY.NLD.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Países Baixos</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1.0827197921178</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1.11656989727557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1.0575296108291</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.884016973125884</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.803923144947343</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.803793907242183</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.796431984708506</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.729660707770887</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.67990209409845</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>0.71694866647548</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>0.75431847325941</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.718390804597701</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.778331257783312</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.75295534974776</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>0.752728641324802</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>8.207</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8.364</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>8.425</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>8.376</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>8.273</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>8.328</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>8.51</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>8.758</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>8.907</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>8.824</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>8.768</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>8.843</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>8.827</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>8.744</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>8.727</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>6.947</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7.115</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>7.166</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>7.129</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>7.02</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>7.045</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>7.178</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>7.383</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>7.518</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>7.441</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>7.383</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>7.429</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>7.381</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>7.259</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>7.228</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>11359.31</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>11536.985</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>11527.464</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>11416.07</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>11436.65</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>11369.142</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>11548.882</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>11858.613</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>12084.615</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>11903.64</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>11799.267</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>11925.13</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>11821.412</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>11761.382</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>11751.396</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9683.639</t>
+          <t>19040682811.0859</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9889.248</t>
+          <t>19984075764.484</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9874.277</t>
+          <t>20771063488.7641</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9784.673</t>
+          <t>25243666885.6993</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9757.916</t>
+          <t>23991048228.482</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9669.388</t>
+          <t>23442113298.1514</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9794.894</t>
+          <t>23777397587.3485</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>10046.648</t>
+          <t>24586017795.294</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>10249.08</t>
+          <t>26746340792.9422</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10080.537</t>
+          <t>28823938933.8462</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>9969.996</t>
+          <t>29795672439.7553</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>10043.639</t>
+          <t>31720812595.2765</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>9909.044</t>
+          <t>29829153267.6334</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>9780.974</t>
+          <t>33925341065.7395</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>9750.111</t>
+          <t>34014734947.789</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>13307667510.7618</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12871978866.151</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13393482078.2862</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>12613499952.0852</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>12047904869.2236</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>11486435653.3957</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>11689850184.3022</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>12159230758.6891</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>13032977189.9364</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>11512246382.3452</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>9310357076.91389</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>9207121401.60207</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>8647662522.27098</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>12158196354.9385</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>12063565652.1724</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1350672.96061874</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1362009.58231543</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1352678.51464639</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1275807.45619909</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1104379.45833477</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1021659.61501624</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>977224.296941785</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>855019.765962058</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>817998.801383675</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1094290.69819987</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1181270.58795882</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1109474.15000841</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1091869.80182562</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1241632.97043629</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1214819.62647668</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>40256.997865659</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40405.5477342736</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>41004.3798801268</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>44409.9068408861</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>48646.0382513431</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>51850.8085051432</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>54963.5238743388</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>63183.4253585911</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>69925.6748551467</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>63276.9334677267</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>69302.4952113669</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>74284.8404818026</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>71616.2775106406</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>70780.0574436329</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>70280.1395939559</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>154712.519881416</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>160851.700009294</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>168189.611354549</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>222454.000251186</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>233736.737008926</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>245215.781761123</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>262759.644006053</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>306762.083946797</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>362216.076482773</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>355234.149117037</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>406825.394919421</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>459949.342291283</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>421426.302590783</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>478820.851454815</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>482306.469140745</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.272326334260384</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.231722829657109</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.262755051876437</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.224269803213305</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.190073651317861</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.158190748481538</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.162102674921093</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.173743158643437</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.213604071377187</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.124364067167709</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.070849981116381</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0908554652328548</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.145863911141362</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.195524260798179</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.191772069624856</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>98628.6376512724</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100712.655399886</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>109942.368802451</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>135061.075511246</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>152031.643711481</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>155546.216502832</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>162310.150846214</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>181761.057710401</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>205275.131643774</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>207078.916718495</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>206496.385875124</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>219625.088051712</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>208851.779194848</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>233792.735302118</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>230690.559561229</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0827197921178</t>
+          <t>1915.59918105107</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656989727557</t>
+          <t>1809.1326586298</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296108291</t>
+          <t>1869.03182783788</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016973125884</t>
+          <t>1769.32247890099</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923144947343</t>
+          <t>1716.22576484666</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793907242183</t>
+          <t>1630.43799196532</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431984708506</t>
+          <t>1628.56647872697</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660707770887</t>
+          <t>1646.92276292687</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990209409845</t>
+          <t>1733.56972465236</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694866647548</t>
+          <t>1547.13699534272</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75431847325941</t>
+          <t>1261.05337625815</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718390804597701</t>
+          <t>1239.34868779137</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778331257783312</t>
+          <t>1171.61123455778</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75295534974776</t>
+          <t>1674.91339784247</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752728641324802</t>
+          <t>1669.00465580692</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>19030607352.7314</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>19327731696.7234</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>19999304490.1934</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>20835013002.1733</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>22123891828.1915</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>22142618921.5009</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>22287887536.6685</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>23316474271.2314</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>22929202489.9516</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>20074737467.5039</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>18351595316.5491</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>18785093798.3799</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>17938637536.4913</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>23718761669.0929</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>23755171653.5368</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>18933531596.0216</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>20094865571.9765</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>20983297099.1883</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>21906332801.5805</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>23023027920.6863</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>22881378638.0226</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>23046316304.8215</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>23803181486.1079</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>23701213900.4513</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>19388542133.1858</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>16338704051.1805</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>16809417532.8112</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>15988882343.4207</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>17025251448.3406</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>17456232147.9331</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>97075756.7097816</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.242</t>
+          <t>-767133875.253103</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>-983992608.994887</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>-1071319799.40725</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.986</t>
+          <t>-899136092.49481</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.052</t>
+          <t>-738759716.521726</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.169</t>
+          <t>-758428768.152975</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>-486707214.876445</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.785</t>
+          <t>-772011410.499714</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.743</t>
+          <t>686195334.318066</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2.668</t>
+          <t>2012891265.36857</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2.806</t>
+          <t>1975676265.56877</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2.594</t>
+          <t>1949755193.07062</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2.687</t>
+          <t>6693510220.75228</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.673</t>
+          <t>6298939505.60368</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>1393.93107816324</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>1389.91531974701</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1377.93427295562</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>1372.51687473699</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1390.01646723647</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1372.51778566359</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1364.57149623851</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1360.78120005418</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>1363.27217345039</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1354.72874613627</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.563</t>
+          <t>1350.39898415278</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>1351.95028940638</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>1342.50703156754</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.659</t>
+          <t>1347.42719382835</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.671</t>
+          <t>1348.93617874931</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1384.10013468951</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1379.36212158146</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>1368.24504145668</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>1362.95004611869</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>1382.40661197531</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>1365.17078395808</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>1357.09536088032</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1354.03210781855</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1356.75480166347</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>1349.00728926254</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>1345.71930910864</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>1348.53894677418</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1339.23321274308</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>1345.08030960611</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>1346.55616851895</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>199181.047434502</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>206201.331602169</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>219671.554623899</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>260826.682657284</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>309331.812342906</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>338770.931733202</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>373715.095330454</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>440915.837777881</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>515397.176063235</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>434382.509740903</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>481023.593405431</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>558261.223095655</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>536286.986960434</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>565838.184619596</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>575067.616934404</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>7767705209.8347</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9148235997.2118</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>9890082189.42219</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>12291436249.4901</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>11646738702.1774</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>11701810763.6206</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>12443740844.0482</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>12966596913.1529</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>15045851860.9432</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>15272342509.2786</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>15753725706.3708</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>17293189007.4784</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>16550175726.8999</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>14830950615.7368</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>15634905605.7855</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>162916.041128828</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>169123.750550774</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>178519.572106297</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>210770.155405717</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>245774.961287897</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>267516.883836512</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>296232.127583162</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>349149.498617249</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>413126.640501725</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>352242.916903994</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>393170.572576715</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>459672.842505908</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>435129.079256136</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>447577.762477819</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>451246.873840881</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11359.31</t>
+          <t>21195334694.959</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11536.985</t>
+          <t>22540221855.6927</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11527.464</t>
+          <t>23244347061.3979</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>11416.07</t>
+          <t>25510519612.3841</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>11436.65</t>
+          <t>25000103739.8513</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11369.142</t>
+          <t>24859859371.7717</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>11548.882</t>
+          <t>25839144194.7934</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>11858.613</t>
+          <t>27308258875.4868</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>12084.615</t>
+          <t>29170432168.5275</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>11903.64</t>
+          <t>27350803718.6969</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>11799.267</t>
+          <t>26507547626.3278</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>11925.13</t>
+          <t>27989172871.0587</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>11821.412</t>
+          <t>26099883963.1295</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>11761.382</t>
+          <t>28687963447.1278</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>11751.396</t>
+          <t>29165447292.8632</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9683.639</t>
+          <t>36265.0063056741</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9889.248</t>
+          <t>37077.5810513949</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9874.277</t>
+          <t>41151.982517602</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>9784.673</t>
+          <t>50056.5272515674</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9757.916</t>
+          <t>63556.8510550091</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9669.388</t>
+          <t>71254.04789669</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>9794.894</t>
+          <t>77482.9677472914</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>10046.648</t>
+          <t>91766.3391606323</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>10249.08</t>
+          <t>102270.535561511</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>10080.537</t>
+          <t>82139.5928369087</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>9969.996</t>
+          <t>87853.0208287156</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>10043.639</t>
+          <t>98588.380589747</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>9909.044</t>
+          <t>101157.907704298</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>9780.974</t>
+          <t>118260.422141777</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>9750.111</t>
+          <t>123820.743093523</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>19040.825</t>
+          <t>-13427629485.1243</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>19985.371</t>
+          <t>-13391985858.4809</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>20773.454</t>
+          <t>-13354264871.9757</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>25244.764</t>
+          <t>-13219083362.894</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>23990.593</t>
+          <t>-13353365037.6739</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>23442.3</t>
+          <t>-13158048608.1511</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>23777.881</t>
+          <t>-13395403350.7452</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>24589.287</t>
+          <t>-14341661962.3339</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>26748.361</t>
+          <t>-14124580307.5843</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>28822.326</t>
+          <t>-12078461209.4183</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>29804.992</t>
+          <t>-10753821919.957</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>31729.883</t>
+          <t>-10695983863.5803</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>29834.984</t>
+          <t>-9549708236.22956</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>33929.876</t>
+          <t>-13857012831.3911</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>34007.727</t>
+          <t>-13530541687.0777</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>153651.9432</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>159159.7628</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>173468.4288</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>213304.728</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>241335.2585</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>253107.1686</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>271849.956</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>311022.6405</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>349420.8976</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>318774.566</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>308701.1763</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>330456.624</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>308256.9248</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>322491.8982</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>322327.3125</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4954.484</t>
+          <t>0.0316074542379907</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5019.95</t>
+          <t>0.031870905717917</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5063.955</t>
+          <t>0.0303112658479399</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5039.554</t>
+          <t>0.0295194175851106</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4993.094</t>
+          <t>0.0334697994091697</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4956.828</t>
+          <t>0.0387705452504724</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4973.707</t>
+          <t>0.0451746810320603</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5063.953</t>
+          <t>0.0483044129804711</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5163.371</t>
+          <t>0.0448888925016633</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5134.333</t>
+          <t>0.0276427593482237</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>5075.677</t>
+          <t>0.0310826447490708</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>5123.12</t>
+          <t>0.0314323285914296</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>5069.102</t>
+          <t>0.0286494754404051</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>5014.898</t>
+          <t>0.0224537137421586</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>4956.517</t>
+          <t>0.025989832493974</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>208523.0192</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>213470.738</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>236419.8576</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>290548.72</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>324147.901</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>329284.6557</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>344034.4</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>398553.7345</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>451851.822</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>434502.5168</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>411344.8245</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>442438.848</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>414484.1888</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>429522.1491</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>436138.579</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>13308.088</t>
+          <t>234886.2576</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12872.534</t>
+          <t>239968.8552</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>13394.602</t>
+          <t>265358.0544</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12614.339</t>
+          <t>325656.6432</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>12047.589</t>
+          <t>363074.5076</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>11486.499</t>
+          <t>370021.4661</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>11690.256</t>
+          <t>387566.052</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>12160.664</t>
+          <t>449384.209</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>13033.611</t>
+          <t>509374.81</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11512.044</t>
+          <t>489392.0812</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>9311.557</t>
+          <t>463243.3281</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>9208.593</t>
+          <t>498962.4</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>8648.76</t>
+          <t>466925.8704</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>12158.885</t>
+          <t>485112.4308</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>12062.644</t>
+          <t>492493.549</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-27.23</t>
+          <t>1194810.4287164</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-23.18</t>
+          <t>1242319.0024956</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-26.28</t>
+          <t>1394372.304</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>1748095.50832</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>1985838.3367039</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>2052235.5097959</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>2169264.20984</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>2468266.2500795</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-21.36</t>
+          <t>2784890.6709292</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>2742650.1937252</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>2668233.0797271</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>2806085.196384</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>2594452.5288</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>2687139.4189281</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-19.17</t>
+          <t>2672996.4671715</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>298475.567058162</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>299553.576606761</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>299829.220307294</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>300682.964657985</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>300898.428012267</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>302419.164272576</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>309844.033405078</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>325080.07784946</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>336084.909433424</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.094</t>
+          <t>328672.500499786</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>322736.3188</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>333055.522326258</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>332583.102857114</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.242</t>
+          <t>331245.174027429</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.214</t>
+          <t>335322.282314508</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>264333.478976782</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>266062.857792493</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>266963.239009168</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>268256.324211491</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>268495.471064747</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>269023.500335721</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>275412.216364162</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>289051.905577404</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>298653.781661261</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>291584.173026864</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>286579.226</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>295139.432989794</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>294985.434565224</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>293395.559014798</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>297014.562427022</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>136393.5536</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>140306.4872</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>152207.5584</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>186663.8368</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>218497.2545</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>235112.5062</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>260305.9696</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>300989.21</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>330285.7896</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>282893.336</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>289432.1268</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>307826.88</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>283181.4832</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>294128.9946</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>300161.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9683639200</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9889247500</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>9874277000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>9784672800</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>9757915600</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>9669387800</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>9794894200</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>10046647600</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10249080200</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>10080536600</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>9969995700</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>10043638700</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>9909044400</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>9780974000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>9750110700</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>11359309805.3968</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11536984784.9073</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>11527464474.2725</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>11416069586.2901</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>11436649900.8717</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>11369142288.8029</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>11548881521.0916</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>11858613200.2748</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>12084615018.4165</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>11903640320.4526</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>11799266902.2646</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>11925129906.3241</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>11821411568.8831</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>11761382227.1958</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>11751395682.6649</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4954484148.23894</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5019950222.35104</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5063954729.11876</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5039553765.94892</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4993093788.96644</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4956828303.82586</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4973707301.612</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5063953146.51523</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5163370847.6249</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5134333145.41473</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>5075677360.27047</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>5123119628.46767</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>5069102011.88042</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>5014897705.7539</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>4956517221.59343</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>8207000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8364000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>8425000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>8376000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>8273000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>8328000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>8510000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>8758000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>8907000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>8824000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>8768000</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>8843000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>8827000</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>8744000</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>8727000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6947000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7115000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>7166000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>7129000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>7020000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>7045000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>7178000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7383000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>7518000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>7441000</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>7383000</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>7429000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>7381000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>7259000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>7228000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>11359309805.3968</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>11536984784.9073</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>11527464474.2725</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>11416069586.2901</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>11436649900.8717</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>11369142288.8029</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>11548881521.0916</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>11858613200.2748</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>12084615018.4165</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>11903640320.4526</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>11799266902.2646</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>11925129906.3241</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>11821411568.8831</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>11761382227.1958</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>11751395682.6649</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>9683639200</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>9889247500</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>9874277000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>9784672800</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>9757915600</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>9669387800</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>9794894200</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>10046647600</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>10249080200</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>10080536600</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>9969995700</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>10043638700</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>9909044400</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>9780974000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>9750110700</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>775867.4092</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>796432.0032</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>860237.8512</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1043978.824</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1189867.4718</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1250410.0752</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1338182.0676</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1551741.7725</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1752836.1956</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1593033.1604</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1562899.5468</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1723872.288</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1613444.1312</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1659468.9186</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1671177.2755</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>371279.8112</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>380275.3424</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>417565.6128</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>512320.48</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>581571.7621</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>605133.9723</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>647872.0216</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>750373.419</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>839660.5996</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>772285.4172</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>752675.4549</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>806789.28</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>750107.3536</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>779241.4254</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>792656.1675</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1493208.28889723</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1547257.99018209</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1603514.76348359</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1640945.06246834</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1665484.59756938</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1678932.79140112</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1717225.65566232</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1751915.83730012</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1794252.52054014</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1848234.69017466</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1858927.4137708</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1830806.70736084</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1797270.97329189</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1785182.08197947</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1760460.69624847</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
